--- a/data/trans_dic/P41E_2023_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes</t>
+          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 18,21</t>
+          <t>11,16; 18,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,31; 18,02</t>
+          <t>12,08; 17,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,09; 16,64</t>
+          <t>12,4; 16,82</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 10,07</t>
+          <t>2,31; 10,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 15,92</t>
+          <t>11,1; 15,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 11,87</t>
+          <t>4,79; 11,98</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 8,86</t>
+          <t>3,63; 8,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,07</t>
+          <t>0,33; 4,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,24</t>
+          <t>1,24; 5,22</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,03; 18,01</t>
+          <t>12,03; 18,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,12; 17,08</t>
+          <t>12,05; 17,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,8; 16,76</t>
+          <t>12,95; 17,02</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 11,89</t>
+          <t>6,33; 12,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,97</t>
+          <t>6,91; 13,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,08</t>
+          <t>7,58; 12,09</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes</t>
+          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39392; 63098</t>
+          <t>38669; 63000</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39903; 58389</t>
+          <t>39157; 56726</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81062; 111600</t>
+          <t>83181; 112795</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17557; 75474</t>
+          <t>17282; 75402</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51635; 74833</t>
+          <t>52174; 73747</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55156; 144706</t>
+          <t>58347; 146125</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8197; 20424</t>
+          <t>8363; 20531</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1686; 17666</t>
+          <t>1436; 17770</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7942; 34796</t>
+          <t>8208; 34701</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51981; 77846</t>
+          <t>52005; 78320</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53261; 75067</t>
+          <t>52951; 76875</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>111606; 146073</t>
+          <t>112854; 148390</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>102485; 209182</t>
+          <t>111245; 214306</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>120512; 216301</t>
+          <t>115136; 216997</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>271699; 413790</t>
+          <t>259713; 414366</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41E_2023_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,16; 18,18</t>
+          <t>10,86; 17,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,08; 17,51</t>
+          <t>11,94; 17,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,4; 16,82</t>
+          <t>12,3; 16,78</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,06</t>
+          <t>7,18; 11,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,1; 15,69</t>
+          <t>11,24; 16,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 11,98</t>
+          <t>9,73; 12,99</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 8,91</t>
+          <t>3,1; 8,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,1</t>
+          <t>1,94; 5,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,22</t>
+          <t>3,01; 5,94</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,03; 18,12</t>
+          <t>11,74; 18,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,05; 17,49</t>
+          <t>12,18; 17,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,95; 17,02</t>
+          <t>13,0; 16,79</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,19</t>
+          <t>9,85; 12,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,91; 13,01</t>
+          <t>11,11; 13,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,09</t>
+          <t>10,88; 12,76</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49459</t>
+          <t>51421</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47761</t>
+          <t>51192</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97220</t>
+          <t>102613</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>38669; 63000</t>
+          <t>39914; 64576</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39157; 56726</t>
+          <t>41176; 61803</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83181; 112795</t>
+          <t>87632; 119524</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>47570</t>
+          <t>51968</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>62695</t>
+          <t>69482</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>110265</t>
+          <t>121450</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17282; 75402</t>
+          <t>40232; 65251</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52174; 73747</t>
+          <t>58121; 84932</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58347; 146125</t>
+          <t>104862; 139952</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>9445</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21088</t>
+          <t>23772</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8363; 20531</t>
+          <t>8312; 21743</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1436; 17770</t>
+          <t>5286; 15063</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8208; 34701</t>
+          <t>16255; 32116</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>64348</t>
+          <t>68709</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>64556</t>
+          <t>70520</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128904</t>
+          <t>139230</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52005; 78320</t>
+          <t>54380; 83359</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52951; 76875</t>
+          <t>58815; 84538</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>112854; 148390</t>
+          <t>122968; 158813</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>174371</t>
+          <t>186425</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>183107</t>
+          <t>200639</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>357478</t>
+          <t>387064</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>111245; 214306</t>
+          <t>163464; 210543</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>115136; 216997</t>
+          <t>179746; 222327</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>259713; 414366</t>
+          <t>356631; 418249</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41E_2023_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
+          <t>Población que con respecto al último año sus relaciones sexuales no han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
+          <t>Población que con respecto al último año sus relaciones sexuales no han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
